--- a/Configs/GameConfig/Datas/Projectile.xlsx
+++ b/Configs/GameConfig/Datas/Projectile.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13380"/>
+    <workbookView windowHeight="17940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -193,6 +193,15 @@
   </si>
   <si>
     <t>直线子弹</t>
+  </si>
+  <si>
+    <t>Muzzle_Fireball</t>
+  </si>
+  <si>
+    <t>Hit_Fireball</t>
+  </si>
+  <si>
+    <t>Projectile_Fireball</t>
   </si>
   <si>
     <t>抛物线子弹</t>
@@ -203,9 +212,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -224,6 +233,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
@@ -232,22 +249,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,14 +323,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -310,6 +341,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -318,44 +357,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -381,67 +390,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,115 +516,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +595,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,30 +671,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -680,145 +689,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1330,8 +1339,17 @@
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
       <c r="I5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1351,13 +1369,22 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
       </c>
       <c r="I6">
         <v>100</v>

--- a/Configs/GameConfig/Datas/Projectile.xlsx
+++ b/Configs/GameConfig/Datas/Projectile.xlsx
@@ -7,7 +7,8 @@
     <workbookView windowHeight="17940"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="子弹逻辑|Projectile" sheetId="1" r:id="rId1"/>
+    <sheet name="子弹资源|ProjectileRes" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -42,7 +43,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -66,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -94,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -111,90 +112,93 @@
     <t>moveType</t>
   </si>
   <si>
+    <t>ProjectileRes</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Gravity</t>
+  </si>
+  <si>
+    <t>DamageSource</t>
+  </si>
+  <si>
+    <t>DamageType</t>
+  </si>
+  <si>
+    <t>DamageInternal</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>移动类型</t>
+  </si>
+  <si>
+    <t>子弹资源</t>
+  </si>
+  <si>
+    <t>子弹速度</t>
+  </si>
+  <si>
+    <t>重力</t>
+  </si>
+  <si>
+    <t>伤害来源</t>
+  </si>
+  <si>
+    <t>伤害类型</t>
+  </si>
+  <si>
+    <t>伤害间隔(ms)</t>
+  </si>
+  <si>
+    <t>直线子弹</t>
+  </si>
+  <si>
+    <t>直线蓝色幽灵子弹</t>
+  </si>
+  <si>
     <t>ShootEffect</t>
   </si>
   <si>
     <t>HitEffect</t>
   </si>
   <si>
-    <t>ProjectileRes</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>Gravity</t>
-  </si>
-  <si>
-    <t>DamageSource</t>
-  </si>
-  <si>
-    <t>DamageType</t>
-  </si>
-  <si>
-    <t>DamageInternal</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>移动类型</t>
-  </si>
-  <si>
     <t>射击特效</t>
   </si>
   <si>
     <t>击中特效</t>
   </si>
   <si>
-    <t>子弹资源</t>
-  </si>
-  <si>
-    <t>子弹速度</t>
-  </si>
-  <si>
-    <t>重力</t>
-  </si>
-  <si>
-    <t>伤害来源</t>
-  </si>
-  <si>
-    <t>伤害类型</t>
-  </si>
-  <si>
-    <t>伤害间隔(ms)</t>
-  </si>
-  <si>
-    <t>直线子弹</t>
-  </si>
-  <si>
     <t>Muzzle_Fireball</t>
   </si>
   <si>
@@ -204,7 +208,16 @@
     <t>Projectile_Fireball</t>
   </si>
   <si>
-    <t>抛物线子弹</t>
+    <t>蓝色幽灵子弹</t>
+  </si>
+  <si>
+    <t>vfx_Muzzle_Orb06_Blue</t>
+  </si>
+  <si>
+    <t>vfx_Hit_Orb06_Blue</t>
+  </si>
+  <si>
+    <t>vfx_Projectile_Orb06_Blue</t>
   </si>
 </sst>
 </file>
@@ -214,8 +227,8 @@
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -227,20 +240,49 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
@@ -248,63 +290,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -323,6 +321,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -339,35 +353,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -375,11 +393,6 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -390,13 +403,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,169 +577,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,9 +614,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,21 +649,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -673,11 +688,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -689,10 +702,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -701,133 +714,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1154,18 +1167,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="5.375" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="21.875" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="8" max="10" width="11.875" customWidth="1"/>
-    <col min="11" max="13" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="15.875" customWidth="1"/>
+    <col min="7" max="8" width="11.875" customWidth="1"/>
+    <col min="9" max="11" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1199,206 +1213,170 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" t="s">
-        <v>14</v>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:11">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
+      <c r="F5">
+        <v>1001</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:11">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
+      <c r="F6">
+        <v>1002</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>9.8</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
         <v>500</v>
       </c>
     </row>
@@ -1407,4 +1385,133 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="5"/>
+  <cols>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="5" max="5" width="17.375" customWidth="1"/>
+    <col min="6" max="6" width="15.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Configs/GameConfig/Datas/Projectile.xlsx
+++ b/Configs/GameConfig/Datas/Projectile.xlsx
@@ -43,7 +43,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="K1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="L1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -118,6 +118,12 @@
     <t>Speed</t>
   </si>
   <si>
+    <t>Distance</t>
+  </si>
+  <si>
+    <t>IsHitDestroy</t>
+  </si>
+  <si>
     <t>Gravity</t>
   </si>
   <si>
@@ -142,6 +148,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -169,6 +178,12 @@
     <t>子弹速度</t>
   </si>
   <si>
+    <t>子弹距离</t>
+  </si>
+  <si>
+    <t>碰撞是否销毁</t>
+  </si>
+  <si>
     <t>重力</t>
   </si>
   <si>
@@ -187,6 +202,9 @@
     <t>直线蓝色幽灵子弹</t>
   </si>
   <si>
+    <t>直线黑色幽灵子弹</t>
+  </si>
+  <si>
     <t>ShootEffect</t>
   </si>
   <si>
@@ -218,6 +236,18 @@
   </si>
   <si>
     <t>vfx_Projectile_Orb06_Blue</t>
+  </si>
+  <si>
+    <t>黑色子弹</t>
+  </si>
+  <si>
+    <t>vfx_Muzzle_BlackHole01_Purple</t>
+  </si>
+  <si>
+    <t>vfx_Hit_BlackHole01_Purple</t>
+  </si>
+  <si>
+    <t>vfx_Projectile_BlackHole01_Purple</t>
   </si>
 </sst>
 </file>
@@ -225,10 +255,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -253,8 +283,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -268,13 +313,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -283,13 +321,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -298,6 +329,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,85 +407,10 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -393,6 +418,11 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -403,43 +433,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,139 +613,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,6 +624,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -608,17 +653,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,17 +672,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -671,16 +699,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -688,9 +716,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,7 +735,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,133 +744,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1167,19 +1197,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="5.375" customWidth="1"/>
     <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="21.875" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="7" max="8" width="11.875" customWidth="1"/>
-    <col min="9" max="11" width="14.5" customWidth="1"/>
+    <col min="7" max="10" width="11.875" customWidth="1"/>
+    <col min="11" max="13" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1213,118 +1243,142 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
+      <c r="M2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="2:13">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1336,27 +1390,33 @@
         <v>30</v>
       </c>
       <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>1</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="2:13">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1368,15 +1428,59 @@
         <v>20</v>
       </c>
       <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>1</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>1</v>
       </c>
-      <c r="K6">
+      <c r="M6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1003</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
         <v>500</v>
       </c>
     </row>
@@ -1390,8 +1494,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="12.875" customWidth="1"/>
     <col min="4" max="4" width="21.25" customWidth="1"/>
@@ -1410,10 +1514,10 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -1421,59 +1525,59 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -1481,16 +1585,16 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:6">
@@ -1498,16 +1602,33 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
